--- a/cosmos-bc-dss/reports/COSMoS_BC_NCIt_Compare.xlsx
+++ b/cosmos-bc-dss/reports/COSMoS_BC_NCIt_Compare.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Compare_Report'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Def_Differ'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Syn_Differ'!$A$1:$G$129</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'No_Green_Match'!$A$1:$H$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Def_Differ'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Syn_Differ'!$A$1:$G$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'No_Green_Match'!$A$1:$H$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12 10:46</t>
+          <t>2026-04-09 10:21</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>531 in scope, 372 matched to green, 159 instrument-specific (no green match)</t>
+          <t>727 in scope, 566 matched to green, 161 instrument-specific (no green match)</t>
         </is>
       </c>
     </row>
@@ -983,11 +983,11 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>BCs with NCIt_Code matched to SDTM CT (of 531 comparable)</t>
+          <t>BCs with NCIt_Code matched to SDTM CT (of 727 comparable)</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>372</v>
+        <v>566</v>
       </c>
       <c r="E2" s="4" t="inlineStr"/>
     </row>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1029,11 +1029,11 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Definitions match (of 372 matched BCs)</t>
+          <t>Definitions match (of 566 matched BCs)</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>369</v>
+        <v>564</v>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
     </row>
@@ -1054,11 +1054,11 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>ALBCREAT (C74761) | HBA1CHGB (C111207) | TUMERGE (C94525)</t>
+          <t>HBA1CHGB (C111207)</t>
         </is>
       </c>
     </row>
@@ -1075,11 +1075,11 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Synonym sets match (of 372 matched BCs)</t>
+          <t>Synonym sets match (of 566 matched BCs)</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>242</v>
+        <v>432</v>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
     </row>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
     </row>
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1219,86 +1219,32 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>C74761</t>
+          <t>C111207</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>ALBCREAT</t>
+          <t>HBA1CHGB</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Albumin To Creatinine Protein Ratio Measurement</t>
+          <t>Hemoglobin A1C to Hemoglobin Ratio Measurement</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>The determination of the ratio of albumin compared to creatinine protein present in a urine sample. The measurement may be expressed as a ratio or percentage.</t>
+          <t>The determination of the ratio of the glycosylated hemoglobin compared to total hemoglobin present in a sample. The measurement may be expressed as a ratio or percentage.</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>The determination of the ratio of albumin compared to creatinine present in a sample. The measurement may be expressed as a ratio or percentage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>C111207</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>HBA1CHGB</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C to Hemoglobin Ratio Measurement</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>The determination of the ratio of the glycosylated hemoglobin compared to total hemoglobin present in a sample. The measurement may be expressed as a ratio or percentage.</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
           <t>The determination of the ratio of the  glycated hemoglobin A1C to total hemoglobin present in a sample. The measurement may be expressed as a ratio or percentage.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>C94525</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>TUMERGE</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Matted Tumor Mass Present</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>A finding indicating that two or more tumors have merged to create a single cancerous mass.</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>A finding indicating the presence of a malignant tumor mass that is formed following the spread of a malignant tumor to two or more adjacent lymph nodes and the resulting fusion and enlargement of the lymph nodes.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1309,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1778,7 +1724,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Albumin To Creatinine Protein Ratio Measurement</t>
+          <t>Albumin to Creatinine Ratio Measurement</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -2286,91 +2232,91 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>C49680</t>
+          <t>C139218</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>FRMSIZE</t>
+          <t>BODYFATP</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Body Frame Size</t>
+          <t>Body Fat Percentage</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Frame Size</t>
+          <t>BODYFATP</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>FRMSIZE</t>
+          <t>BODYFATP; Body Fat Percentage; Total Body Fat/Total Body Mass</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: frmsize ||| YELLOW_ONLY: frame size</t>
+          <t>GREEN_ONLY: body fat percentage ; total body fat/total body mass</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>C16358</t>
+          <t>C49680</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>FRMSIZE</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Body Mass Index</t>
+          <t>Body Frame Size</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>BMI;Quetelet Index</t>
+          <t>Frame Size</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>BMI; Body mass index; Body mass index (BMI) [Ratio]; Quetelet Index; Vital Signs – BMI</t>
+          <t>FRMSIZE</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: body mass index ; body mass index (bmi) [ratio] ; vital signs – bmi</t>
+          <t>GREEN_ONLY: frmsize ||| YELLOW_ONLY: frame size</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>C174446</t>
+          <t>C16358</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>TEMP</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Body Temperature</t>
+          <t>Body Mass Index</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -2380,34 +2326,34 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>BMI;Quetelet Index</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>TEMP; Temperature; Temperature in Celsius or Fahrenheit; body temperature; body_temperature</t>
+          <t>BMI; Body mass index; Body mass index (BMI) [Ratio]; Quetelet Index; Vital Signs – BMI</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: body temperature ; body_temperature ; temp ; temperature in celsius or fahrenheit</t>
+          <t>GREEN_ONLY: body mass index ; body mass index (bmi) [ratio] ; vital signs – bmi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>C61545</t>
+          <t>C25157</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>BMD</t>
+          <t>BSA</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Bone Mineral Density Test</t>
+          <t>Body Surface Area</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -2417,34 +2363,34 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>BMD;Bone Mineral Density;Bone Mass;Bone Density</t>
+          <t>BSA</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>BMD; Bone Density Test; Bone Mineral Density; bone density; bone mass</t>
+          <t>BSA; Vital Signs – BSA; body surface area; body_surface_area</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: bone density test</t>
+          <t>GREEN_ONLY: body surface area ; body_surface_area ; vital signs – bsa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>C64548</t>
+          <t>C174446</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>CRP</t>
+          <t>TEMP</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>C-Reactive Protein Measurement</t>
+          <t>Body Temperature</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2454,71 +2400,71 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>CRP;C Reactive Protein</t>
+          <t>Temperature</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>C Reactive Protein; C-Reactive Protein; CRP</t>
+          <t>TEMP; Temperature; Temperature in Celsius or Fahrenheit; body temperature; body_temperature</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: c-reactive protein</t>
+          <t>GREEN_ONLY: body temperature ; body_temperature ; temp ; temperature in celsius or fahrenheit</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>C139084</t>
+          <t>C61545</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>CMONOX</t>
+          <t>BMD</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Carbon Monoxide Measurement</t>
+          <t>Bone Mineral Density Test</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Carbon Monoxide;CO</t>
+          <t>BMD;Bone Mineral Density;Bone Mass;Bone Density</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>CMONOX; Carbon Monoxide</t>
+          <t>BMD; Bone Density Test; Bone Mineral Density; bone density; bone mass</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: cmonox ||| YELLOW_ONLY: co</t>
+          <t>GREEN_ONLY: bone density test</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>C96591</t>
+          <t>C64548</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>CARBXHGB</t>
+          <t>CRP</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Carboxyhemoglobin Measurement</t>
+          <t>C-Reactive Protein Measurement</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2528,71 +2474,71 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Carboxyhemoglobin</t>
+          <t>CRP;C Reactive Protein</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>CARBXHGB; Carboxyhemoglobin</t>
+          <t>C Reactive Protein; C-Reactive Protein; CRP</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: carbxhgb</t>
+          <t>GREEN_ONLY: c-reactive protein</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>C122187</t>
+          <t>C168125</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>CABNIND</t>
+          <t>CPLRFLT</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Congenital Abnormality Indicator</t>
+          <t>Capillary Refill Test</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>CABNIND;Abnormal Indicator</t>
+          <t>Capillary Refill Time;CPLRFLT</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>CABNIND</t>
+          <t>CPLRFLT; Capillary Refill Time; Examination of the Extremities – Capillary Refill Time</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: abnormal indicator</t>
+          <t>GREEN_ONLY: examination of the extremities – capillary refill time</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>C181330</t>
+          <t>C139084</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>CPNUMVAR</t>
+          <t>CMONOX</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Copy Number Variation Assessment</t>
+          <t>Carbon Monoxide Measurement</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2602,34 +2548,34 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>CPNUMVAR;Gene Copy Number Variation;Copy Number Variation Assessment</t>
+          <t>Carbon Monoxide;CO</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>CPNUMVAR; Copy Number Variation; Gene Copy Number Variation; Gene Copy Number Variation Assessment</t>
+          <t>CMONOX; Carbon Monoxide</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: copy number variation ; gene copy number variation assessment ||| YELLOW_ONLY: copy number variation assessment</t>
+          <t>GREEN_ONLY: cmonox ||| YELLOW_ONLY: co</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>C64547</t>
+          <t>C96591</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>CREAT</t>
+          <t>CARBXHGB</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Creatinine Measurement</t>
+          <t>Carboxyhemoglobin Measurement</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2639,34 +2585,34 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Creatinine</t>
+          <t>Carboxyhemoglobin</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>CREAT; Cr; Creatinine; Creatinine Level</t>
+          <t>CARBXHGB; Carboxyhemoglobin</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: cr ; creat ; creatinine level</t>
+          <t>GREEN_ONLY: carbxhgb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>C82621</t>
+          <t>C122187</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>DDIMER</t>
+          <t>CABNIND</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>D-Dimer Measurement</t>
+          <t>Congenital Abnormality Indicator</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2676,145 +2622,145 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>D-Dimer;DDIMER;FDP;Fibrin Degragation Products</t>
+          <t>CABNIND;Abnormal Indicator</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>D-Dimer; DDIMER</t>
+          <t>CABNIND</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: fdp ; fibrin degragation products</t>
+          <t>YELLOW_ONLY: abnormal indicator</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>C25299</t>
+          <t>C181330</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>DIABP</t>
+          <t>CPNUMVAR</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Diastolic Blood Pressure</t>
+          <t>Copy Number Variation Assessment</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>DIABP</t>
+          <t>CPNUMVAR;Gene Copy Number Variation;Copy Number Variation Assessment</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>DIABP; Diastolic Pressure; Diastolic blood pressure</t>
+          <t>CPNUMVAR; Copy Number Variation; Gene Copy Number Variation; Gene Copy Number Variation Assessment</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: diastolic blood pressure ; diastolic pressure</t>
+          <t>GREEN_ONLY: copy number variation ; gene copy number variation assessment ||| YELLOW_ONLY: copy number variation assessment</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>C81974</t>
+          <t>C64547</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ANGLOBDR</t>
+          <t>CREAT</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Direct Antiglobulin Test</t>
+          <t>Creatinine Measurement</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>ANGLOBDR;Antiglobulin Test Polyspecific, Direct;Antiglobulin Test, Direct;DAT;Direct Anti-human Globulin Test;Direct Antiglobulin Test;Direct Coombs Test</t>
+          <t>Creatinine</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>ANGLOBDR; Antibody detection, red blood cell, enzyme, 1 stage technique, including anti-human globulin; Antiglobulin Test Polyspecific, Direct; Antiglobulin Test, Direct; DAT; Direct Anti-human Globulin Test; Direct Coombs Test</t>
+          <t>CREAT; Cr; Creatinine; Creatinine Level</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: antibody detection, red blood cell, enzyme, 1 stage technique, including anti-human globulin ||| YELLOW_ONLY: direct antiglobulin test</t>
+          <t>GREEN_ONLY: cr ; creat ; creatinine level</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>C117807</t>
+          <t>C82621</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>TECHQUAL</t>
+          <t>DDIMER</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>ECG Technical Quality</t>
+          <t>D-Dimer Measurement</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>TECHQUAL</t>
+          <t>D-Dimer;DDIMER;FDP;Fibrin Degragation Products</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>TECHQUAL; Technical Quality</t>
+          <t>D-Dimer; DDIMER</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: technical quality</t>
+          <t>YELLOW_ONLY: fdp ; fibrin degragation products</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>C17953</t>
+          <t>C25299</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>EDULEVEL</t>
+          <t>DIABP</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Education Level</t>
+          <t>Diastolic Blood Pressure</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -2824,71 +2770,71 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>EDULEVEL;Education Level Completed;Education</t>
+          <t>DIABP</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>EDULEVEL; Education; Education Level Completed; Educational Attainment; Educational Level; Level of Education Attained; education level; education_level</t>
+          <t>DIABP; Diastolic Pressure; Diastolic blood pressure</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: education level ; education_level ; educational attainment ; educational level ; level of education attained</t>
+          <t>GREEN_ONLY: diastolic blood pressure ; diastolic pressure</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>C64550</t>
+          <t>C81974</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>EOS</t>
+          <t>ANGLOBDR</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Eosinophil Count</t>
+          <t>Direct Antiglobulin Test</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Eosinophils</t>
+          <t>ANGLOBDR;Antiglobulin Test Polyspecific, Direct;Antiglobulin Test, Direct;DAT;Direct Anti-human Globulin Test;Direct Antiglobulin Test;Direct Coombs Test</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>EOS; Eosinophil; Eosinophils</t>
+          <t>ANGLOBDR; Antibody detection, red blood cell, enzyme, 1 stage technique, including anti-human globulin; Antiglobulin Test Polyspecific, Direct; Antiglobulin Test, Direct; DAT; Direct Anti-human Globulin Test; Direct Coombs Test</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: eos ; eosinophil</t>
+          <t>GREEN_ONLY: antibody detection, red blood cell, enzyme, 1 stage technique, including anti-human globulin ||| YELLOW_ONLY: direct antiglobulin test</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>C51946</t>
+          <t>C117807</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>TECHQUAL</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Erythrocyte Count</t>
+          <t>ECG Technical Quality</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -2898,108 +2844,108 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>RBC;Red Blood Cells</t>
+          <t>TECHQUAL</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Erythrocytes; RBC; Red Blood Cell Count; Red Blood Cells; Red Cell Count</t>
+          <t>TECHQUAL; Technical Quality</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: erythrocytes ; red blood cell count ; red cell count</t>
+          <t>GREEN_ONLY: technical quality</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>C64797</t>
+          <t>C17953</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>MCH</t>
+          <t>EDULEVEL</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Erythrocyte Mean Corpuscular Hemoglobin</t>
+          <t>Education Level</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>RBC Mean Corpuscular Hemoglobin;MCH</t>
+          <t>EDULEVEL;Education Level Completed;Education</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Ery. Mean Corpuscular Hemoglobin; MCH</t>
+          <t>EDULEVEL; Education; Education Level Completed; Educational Attainment; Educational Level; Level of Education Attained; education level; education_level</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: ery. mean corpuscular hemoglobin ||| YELLOW_ONLY: rbc mean corpuscular hemoglobin</t>
+          <t>GREEN_ONLY: education level ; education_level ; educational attainment ; educational level ; level of education attained</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>C64798</t>
+          <t>C64550</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>MCHC</t>
+          <t>EOS</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Erythrocyte Mean Corpuscular Hemoglobin Concentration</t>
+          <t>Eosinophil Count</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>RBC Mean Corpuscular Hemoglobin Concentration;MCHC</t>
+          <t>Eosinophils</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Ery. Mean Corpuscular HGB Concentration; MCHC</t>
+          <t>EOS; Eosinophil; Eosinophils</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: ery. mean corpuscular hgb concentration ||| YELLOW_ONLY: rbc mean corpuscular hemoglobin concentration</t>
+          <t>GREEN_ONLY: eos ; eosinophil</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>C64799</t>
+          <t>C51946</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>MCV</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Erythrocyte Mean Corpuscular Volume</t>
+          <t>Erythrocyte Count</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3009,108 +2955,108 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>RBC Mean Corpuscular Volume;MCV</t>
+          <t>RBC;Red Blood Cells</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Ery. Mean Corpuscular Volume; Erythrocytes Mean Corpuscular Volume; MCV; RBC Mean Corpuscular Volume</t>
+          <t>Erythrocytes; RBC; Red Blood Cell Count; Red Blood Cells; Red Cell Count</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: ery. mean corpuscular volume ; erythrocytes mean corpuscular volume</t>
+          <t>GREEN_ONLY: erythrocytes ; red blood cell count ; red cell count</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>C81247</t>
+          <t>C64797</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>EDLVRDTC</t>
+          <t>MCH</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Expected Date of Confinement</t>
+          <t>Erythrocyte Mean Corpuscular Hemoglobin</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>EDLVRDTC;EDD;EDC;Estimated Date of Delivery;Estimated Date of Confinement;Estimated Due Date</t>
+          <t>RBC Mean Corpuscular Hemoglobin;MCH</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Due Date; EDC; EDD; EDLVRDTC; Estimated Date of Confinement; Estimated Date of Delivery; Estimated Due Date</t>
+          <t>Ery. Mean Corpuscular Hemoglobin; MCH</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: due date</t>
+          <t>GREEN_ONLY: ery. mean corpuscular hemoglobin ||| YELLOW_ONLY: rbc mean corpuscular hemoglobin</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>C170598</t>
+          <t>C64798</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>T4FRIDX</t>
+          <t>MCHC</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Free Thyroxine Index</t>
+          <t>Erythrocyte Mean Corpuscular Hemoglobin Concentration</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>T4FRIDX</t>
+          <t>RBC Mean Corpuscular Hemoglobin Concentration;MCHC</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>T4FRIDX; Thyroxine, Free Index</t>
+          <t>Ery. Mean Corpuscular HGB Concentration; MCHC</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: thyroxine, free index</t>
+          <t>GREEN_ONLY: ery. mean corpuscular hgb concentration ||| YELLOW_ONLY: rbc mean corpuscular hemoglobin concentration</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>C74786</t>
+          <t>C64799</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>T4FR</t>
+          <t>MCV</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Free Thyroxine Measurement</t>
+          <t>Erythrocyte Mean Corpuscular Volume</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3120,34 +3066,34 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Free T4;T4FR</t>
+          <t>RBC Mean Corpuscular Volume;MCV</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Free T4; T4-Free; T4FR; Thyroxine, Free</t>
+          <t>Ery. Mean Corpuscular Volume; Erythrocytes Mean Corpuscular Volume; MCV; RBC Mean Corpuscular Volume</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: t4-free ; thyroxine, free</t>
+          <t>GREEN_ONLY: ery. mean corpuscular volume ; erythrocytes mean corpuscular volume</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>C181333</t>
+          <t>C81247</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>GENESIG</t>
+          <t>EDLVRDTC</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Gene Signature Assessment</t>
+          <t>Expected Date of Confinement</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3157,34 +3103,34 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>GENESIG;Gene Expression Profile;Gene Expression Signature</t>
+          <t>EDLVRDTC;EDD;EDC;Estimated Date of Delivery;Estimated Date of Confinement;Estimated Due Date</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>GENESIG; Gene Expression Profile; Gene Expression Signature; Gene Signature</t>
+          <t>Due Date; EDC; EDD; EDLVRDTC; Estimated Date of Confinement; Estimated Date of Delivery; Estimated Due Date</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: gene signature</t>
+          <t>GREEN_ONLY: due date</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>C105585</t>
+          <t>C170598</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>GLUC</t>
+          <t>T4FRIDX</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Glucose Measurement</t>
+          <t>Free Thyroxine Index</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -3194,71 +3140,71 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Glucose</t>
+          <t>T4FRIDX</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>GLUC; Glucose</t>
+          <t>T4FRIDX; Thyroxine, Free Index</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: gluc</t>
+          <t>GREEN_ONLY: thyroxine, free index</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>C135522</t>
+          <t>C74786</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>GRFTSTAT</t>
+          <t>T4FR</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Graft Status</t>
+          <t>Free Thyroxine Measurement</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Graft Status;GRFTSTAT</t>
+          <t>Free T4;T4FR</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>GRFTSTAT</t>
+          <t>Free T4; T4-Free; T4FR; Thyroxine, Free</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: graft status</t>
+          <t>GREEN_ONLY: t4-free ; thyroxine, free</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>C49677</t>
+          <t>C181333</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>GENESIG</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Heart Rate</t>
+          <t>Gene Signature Assessment</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -3268,34 +3214,34 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>GENESIG;Gene Expression Profile;Gene Expression Signature</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>HR; Heart rate; Vital Signs – Heart Rate</t>
+          <t>GENESIG; Gene Expression Profile; Gene Expression Signature; Gene Signature</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: heart rate ; vital signs – heart rate</t>
+          <t>GREEN_ONLY: gene signature</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>C64796</t>
+          <t>C105585</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>HCT</t>
+          <t>GLUC</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Hematocrit Measurement</t>
+          <t>Glucose Measurement</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3305,71 +3251,71 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Hematocrit;Packed Cell Volume;PCV;Erythrocyte Volume Fraction;EVF</t>
+          <t>Glucose</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>EVF; Erythrocyte Volume Fraction; HCT; Hematocrit; PCV; Packed Cell Volume</t>
+          <t>GLUC; Glucose</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: hct</t>
+          <t>GREEN_ONLY: gluc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>C64849</t>
+          <t>C135522</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>HBA1C</t>
+          <t>GRFTSTAT</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C Measurement</t>
+          <t>Graft Status</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C;HBA1C;Glycosylated Hemoglobin A1C</t>
+          <t>Graft Status;GRFTSTAT</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>HBA1C; Hb A1c Measurement; HbA1c Measurement; Hemoglobin A1C</t>
+          <t>GRFTSTAT</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: hb a1c measurement ; hba1c measurement ||| YELLOW_ONLY: glycosylated hemoglobin a1c</t>
+          <t>YELLOW_ONLY: graft status</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>C111207</t>
+          <t>C49677</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>HBA1CHGB</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C to Hemoglobin Ratio Measurement</t>
+          <t>Heart Rate</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3379,34 +3325,34 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C/Hemoglobin;HBA1CHGB</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Glycated Hemoglobin/Hemoglobin; HBA1CHGB; HbA1c/Hemoglobin; Hemoglobin A1C/Hemoglobin</t>
+          <t>HR; Heart rate; Vital Signs – Heart Rate</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: glycated hemoglobin/hemoglobin ; hba1c/hemoglobin</t>
+          <t>GREEN_ONLY: heart rate ; vital signs – heart rate</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>C64848</t>
+          <t>C64796</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>HGB</t>
+          <t>HCT</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Hemoglobin Measurement</t>
+          <t>Hematocrit Measurement</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -3416,71 +3362,71 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Hemoglobin;HGB</t>
+          <t>Hematocrit;Packed Cell Volume;PCV;Erythrocyte Volume Fraction;EVF</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>HGB; Hemoglobin; Hemoglobin Monomer</t>
+          <t>EVF; Erythrocyte Volume Fraction; HCT; Hematocrit; PCV; Packed Cell Volume</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: hemoglobin monomer</t>
+          <t>GREEN_ONLY: hct</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>C105587</t>
+          <t>C64849</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>HDL</t>
+          <t>HBA1C</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>High Density Lipoprotein Cholesterol Measurement</t>
+          <t>Hemoglobin A1C Measurement</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>HDL;HDL Cholesterol</t>
+          <t>Hemoglobin A1C;HBA1C;Glycosylated Hemoglobin A1C</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>HDL; HDL Cholesterol; HDL Cholesterol Measurement; High-Density Lipoprotein Cholesterol Measurement</t>
+          <t>HBA1C; Hb A1c Measurement; HbA1c Measurement; Hemoglobin A1C</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: hdl cholesterol measurement ; high-density lipoprotein cholesterol measurement</t>
+          <t>GREEN_ONLY: hb a1c measurement ; hba1c measurement ||| YELLOW_ONLY: glycosylated hemoglobin a1c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>C112312</t>
+          <t>C111207</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>HER2</t>
+          <t>HBA1CHGB</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Human Epidermal Growth Factor Receptor 2 Measurement</t>
+          <t>Hemoglobin A1C to Hemoglobin Ratio Measurement</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -3490,71 +3436,71 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>ERBB2;HER2;HER2/NEU;Receptor Tyrosine-Protein Kinase erbB-2 Measurement</t>
+          <t>Hemoglobin A1C/Hemoglobin;HBA1CHGB</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>ERBB2; HER2; HER2/NEU; Human Epidermal Growth Factor Receptor 2; Receptor Tyrosine-Protein Kinase erbB-2 Measurement</t>
+          <t>Glycated Hemoglobin/Hemoglobin; HBA1CHGB; HbA1c/Hemoglobin; Hemoglobin A1C/Hemoglobin</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: human epidermal growth factor receptor 2</t>
+          <t>GREEN_ONLY: glycated hemoglobin/hemoglobin ; hba1c/hemoglobin</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>C91372</t>
+          <t>C64848</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ANGLBIND</t>
+          <t>HGB</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Indirect Antiglobulin Test</t>
+          <t>Hemoglobin Measurement</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>ANGLBIND;Indirect Coombs Test;Indirect Anti-human Globulin Test;Antiglobulin Test Indirect</t>
+          <t>Hemoglobin;HGB</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>ANGLBIND; Antibody detection, RBC, enzyme, 2 stage technique, including anti-human globulin; Antiglobulin Test, Indirect; Indirect Anti-human Globulin Test; Indirect Coombs Test</t>
+          <t>HGB; Hemoglobin; Hemoglobin Monomer</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: antibody detection, rbc, enzyme, 2 stage technique, including anti-human globulin ; antiglobulin test, indirect ||| YELLOW_ONLY: antiglobulin test indirect</t>
+          <t>GREEN_ONLY: hemoglobin monomer</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>C176287</t>
+          <t>C105587</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>INFOSCOD</t>
+          <t>HDL</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Information Source for Cause of Death</t>
+          <t>High Density Lipoprotein Cholesterol Measurement</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -3564,71 +3510,71 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>INFOSCOD;cause of death source</t>
+          <t>HDL;HDL Cholesterol</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>INFOSCOD; cause of death source; cause_of_death_source</t>
+          <t>HDL; HDL Cholesterol; HDL Cholesterol Measurement; High-Density Lipoprotein Cholesterol Measurement</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: cause_of_death_source</t>
+          <t>GREEN_ONLY: hdl cholesterol measurement ; high-density lipoprotein cholesterol measurement</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>C181499</t>
+          <t>C112312</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>ISOMSER</t>
+          <t>HER2</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Isometric Muscle Strength, External Rotation</t>
+          <t>Human Epidermal Growth Factor Receptor 2 Measurement</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>ISOMSER;Isometric Muscle Strength, External Rotation</t>
+          <t>ERBB2;HER2;HER2/NEU;Receptor Tyrosine-Protein Kinase erbB-2 Measurement</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>ISOMSER; Isometric Muscle Strength, Extern Rotat</t>
+          <t>ERBB2; ErbB-2; HER2; HER2/NEU; Human Epidermal Growth Factor Receptor 2; Receptor Tyrosine-Protein Kinase erbB-2 Measurement</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: isometric muscle strength, extern rotat ||| YELLOW_ONLY: isometric muscle strength, external rotation</t>
+          <t>GREEN_ONLY: erbb-2 ; human epidermal growth factor receptor 2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>C181498</t>
+          <t>C91372</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>ISOMSIR</t>
+          <t>ANGLBIND</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Isometric Muscle Strength, Internal Rotation</t>
+          <t>Indirect Antiglobulin Test</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -3638,34 +3584,34 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>ISOMSIR;Isometric Muscle Strength, Internal Rotation</t>
+          <t>ANGLBIND;Indirect Coombs Test;Indirect Anti-human Globulin Test;Antiglobulin Test Indirect</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>ISOMSIR; Isometric Muscle Strength, Intern Rotat</t>
+          <t>ANGLBIND; Antibody detection, RBC, enzyme, 2 stage technique, including anti-human globulin; Antiglobulin Test, Indirect; Indirect Anti-human Globulin Test; Indirect Coombs Test</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: isometric muscle strength, intern rotat ||| YELLOW_ONLY: isometric muscle strength, internal rotation</t>
+          <t>GREEN_ONLY: antibody detection, rbc, enzyme, 2 stage technique, including anti-human globulin ; antiglobulin test, indirect ||| YELLOW_ONLY: antiglobulin test indirect</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>C64855</t>
+          <t>C176287</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>LDH</t>
+          <t>INFOSCOD</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Lactate Dehydrogenase Measurement</t>
+          <t>Information Source for Cause of Death</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3675,108 +3621,108 @@
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Lactate Dehydrogenase;LDH</t>
+          <t>INFOSCOD;cause of death source</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>LDH; LDH Measurement; Lactate Dehydrogenase</t>
+          <t>INFOSCOD; cause of death source; cause_of_death_source</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: ldh measurement</t>
+          <t>GREEN_ONLY: cause_of_death_source</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>C51948</t>
+          <t>C181499</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>WBC</t>
+          <t>ISOMSER</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Leukocyte Count</t>
+          <t>Isometric Muscle Strength, External Rotation</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>WBC;White Blood Cells</t>
+          <t>ISOMSER;Isometric Muscle Strength, External Rotation</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Leukocytes; WBC; White Blood Cell Count; White Blood Cells; White Cell Count</t>
+          <t>ISOMSER; Isometric Muscle Strength, Extern Rotat</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: leukocytes ; white blood cell count ; white cell count</t>
+          <t>GREEN_ONLY: isometric muscle strength, extern rotat ||| YELLOW_ONLY: isometric muscle strength, external rotation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>C124331</t>
+          <t>C181498</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>LOCDTH</t>
+          <t>ISOMSIR</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Location of Death</t>
+          <t>Isometric Muscle Strength, Internal Rotation</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>LOCDTH;Location of Death</t>
+          <t>ISOMSIR;Isometric Muscle Strength, Internal Rotation</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>LOCDTH</t>
+          <t>ISOMSIR; Isometric Muscle Strength, Intern Rotat</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: location of death</t>
+          <t>GREEN_ONLY: isometric muscle strength, intern rotat ||| YELLOW_ONLY: isometric muscle strength, internal rotation</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>C96684</t>
+          <t>C64855</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>LDIAM</t>
+          <t>LDH</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Longest Diameter</t>
+          <t>Lactate Dehydrogenase Measurement</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -3786,34 +3732,34 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>LDIAM</t>
+          <t>Lactate Dehydrogenase;LDH</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Greatest Diameter; LDIAM; LONGEST_DIAM_DIM1; longest dimension; longest measurement; longest_dimension; longest_measurement</t>
+          <t>LDH; LDH Measurement; Lactate Dehydrogenase</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: greatest diameter ; longest dimension ; longest measurement ; longest_diam_dim1 ; longest_dimension ; longest_measurement</t>
+          <t>GREEN_ONLY: ldh measurement</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>C105588</t>
+          <t>C139219</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>LDL</t>
+          <t>LBMTBMR</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Low Density Lipoprotein Cholesterol Measurement</t>
+          <t>Lean Body Mass to Total Body Mass Ratio</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -3823,34 +3769,34 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>LDL;LDL Cholesterol</t>
+          <t>LBMTBMR</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>LDL; LDL Cholesterol; LDL Cholesterol Measurement; LDL-C Measurement; LDL-Cholesterol Measurement; Low Density Lipoprotein-Cholesterol Measurement; Low-Density Lipoprotein Cholesterol Measurement; Low-Density Lipoprotein-Cholesterol Measurement</t>
+          <t>LBMTBMR; Lean Body Mass/Total Body Mass</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: ldl cholesterol measurement ; ldl-c measurement ; ldl-cholesterol measurement ; low density lipoprotein-cholesterol measurement ; low-density lipoprotein cholesterol measurement ; low-density lipoprotein-cholesterol measurement</t>
+          <t>GREEN_ONLY: lean body mass/total body mass</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>C124448</t>
+          <t>C51948</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>LNSTATE</t>
+          <t>WBC</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Lymph Node State</t>
+          <t>Leukocyte Count</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -3860,71 +3806,71 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>LNSTATE</t>
+          <t>WBC;White Blood Cells</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>LNSTATE; Lymph Node Status</t>
+          <t>Leukocytes; WBC; White Blood Cell Count; White Blood Cells; White Cell Count</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: lymph node status</t>
+          <t>GREEN_ONLY: leukocytes ; white blood cell count ; white cell count</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>C51949</t>
+          <t>C124331</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>LYM</t>
+          <t>LOCDTH</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Lymphocyte Count</t>
+          <t>Location of Death</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Lymphocytes</t>
+          <t>LOCDTH;Location of Death</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>LYM; Lymphocytes</t>
+          <t>LOCDTH</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: lym</t>
+          <t>YELLOW_ONLY: location of death</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>C98869</t>
+          <t>C96684</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>PLSMCECE</t>
+          <t>LDIAM</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Mature Plasma Cell to Total Cell Ratio Measurement</t>
+          <t>Longest Diameter</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -3934,71 +3880,71 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>PLSMCECE;Mature Plasma Cells/Total Cells</t>
+          <t>LDIAM</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>Mature Plasma Cells to Total Cells Ratio Measurement; Mature Plasma Cells/Total Cells; PLSMCECE</t>
+          <t>Greatest Diameter; LDIAM; LONGEST_DIAM_DIM1; longest dimension; longest measurement; longest_dimension; longest_measurement</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: mature plasma cells to total cells ratio measurement</t>
+          <t>GREEN_ONLY: greatest diameter ; longest dimension ; longest measurement ; longest_diam_dim1 ; longest_dimension ; longest_measurement</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>C119259</t>
+          <t>C105588</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>EGHRMN</t>
+          <t>LDL</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Mean Heart Rate by Electrocardiogram</t>
+          <t>Low Density Lipoprotein Cholesterol Measurement</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>ECG Mean Heart Rate;EKG Mean Heart Rate;EGHRMN</t>
+          <t>LDL;LDL Cholesterol</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>ECG Mean Heart Rate; EGHRMN</t>
+          <t>LDL; LDL Cholesterol; LDL Cholesterol Measurement; LDL-C Measurement; LDL-Cholesterol Measurement; Low Density Lipoprotein-Cholesterol Measurement; Low-Density Lipoprotein Cholesterol Measurement; Low-Density Lipoprotein-Cholesterol Measurement</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: ekg mean heart rate</t>
+          <t>GREEN_ONLY: ldl cholesterol measurement ; ldl-c measurement ; ldl-cholesterol measurement ; low density lipoprotein-cholesterol measurement ; low-density lipoprotein cholesterol measurement ; low-density lipoprotein-cholesterol measurement</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>C106541</t>
+          <t>C124448</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>MENOSTAT</t>
+          <t>LNSTATE</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Menopause Status</t>
+          <t>Lymph Node State</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -4008,34 +3954,34 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>MENOSTAT</t>
+          <t>LNSTATE</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>MENOSTAT; Menopausal Status; menopause status; menopause_status</t>
+          <t>LNSTATE; Lymph Node Status</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: menopausal status ; menopause status ; menopause_status</t>
+          <t>GREEN_ONLY: lymph node status</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>C187786</t>
+          <t>C51949</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>MBIMAB</t>
+          <t>LYM</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Microbial-induced IgM Antibody Measurement</t>
+          <t>Lymphocyte Count</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -4045,34 +3991,34 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>MBIMAB;Microbial-induced IgM Antibody</t>
+          <t>Lymphocytes</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>MBIMAB; Microbe-induced IgM Antibody Measurement; Microbial-induced IgM Antibody</t>
+          <t>LYM; Lymphocytes</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: microbe-induced igm antibody measurement</t>
+          <t>GREEN_ONLY: lym</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>C122191</t>
+          <t>C98869</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>MSCRGIND</t>
+          <t>PLSMCECE</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Miscarriage Indicator</t>
+          <t>Mature Plasma Cell to Total Cell Ratio Measurement</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
@@ -4082,71 +4028,71 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>MSCRGIND</t>
+          <t>PLSMCECE;Mature Plasma Cells/Total Cells</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>MSCRGIND; Spontaneous Abortion Indicator</t>
+          <t>Mature Plasma Cells to Total Cells Ratio Measurement; Mature Plasma Cells/Total Cells; PLSMCECE</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: spontaneous abortion indicator</t>
+          <t>GREEN_ONLY: mature plasma cells to total cells ratio measurement</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>C64823</t>
+          <t>C119259</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>MONO</t>
+          <t>EGHRMN</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Monocyte Count</t>
+          <t>Mean Heart Rate by Electrocardiogram</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Monocytes</t>
+          <t>ECG Mean Heart Rate;EKG Mean Heart Rate;EGHRMN</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>MONO; Monocytes</t>
+          <t>ECG Mean Heart Rate; EGHRMN</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: mono</t>
+          <t>YELLOW_ONLY: ekg mean heart rate</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>C64830</t>
+          <t>C106541</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>NEUTB</t>
+          <t>MENOSTAT</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Neutrophil Band Form Count</t>
+          <t>Menopause Status</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -4156,34 +4102,34 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Neutrophil Bands;Bands;NEUTB</t>
+          <t>MENOSTAT</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Bands; NEUTB; Neutrophil Bands; Neutrophils Band Form</t>
+          <t>MENOSTAT; Menopausal Status; menopause status; menopause_status</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: neutrophils band form</t>
+          <t>GREEN_ONLY: menopausal status ; menopause status ; menopause_status</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>C147406</t>
+          <t>C187786</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>NORNCTN</t>
+          <t>MBIMAB</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Nornicotine Measurement</t>
+          <t>Microbial-induced IgM Antibody Measurement</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -4193,34 +4139,34 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Nornicotine</t>
+          <t>MBIMAB;Microbial-induced IgM Antibody</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>NORNCTN; Nornicotine</t>
+          <t>MBIMAB; Microbe-induced IgM Antibody Measurement; Microbial-induced IgM Antibody</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: nornctn</t>
+          <t>GREEN_ONLY: microbe-induced igm antibody measurement</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>C106551</t>
+          <t>C122191</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>PREGNN</t>
+          <t>MSCRGIND</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Number of Pregnancies</t>
+          <t>Miscarriage Indicator</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -4230,108 +4176,108 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>PREGNN;Maternal Gravity;Pregnancy Count;Total Number of Pregnancies</t>
+          <t>MSCRGIND</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>Maternal Gravity; PREGNN; Total Number of Pregnancies; number of pregnancies; number_of_pregnancies; pregnancy count; pregnancy_count</t>
+          <t>MSCRGIND; Spontaneous Abortion Indicator</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: number of pregnancies ; number_of_pregnancies ; pregnancy_count</t>
+          <t>GREEN_ONLY: spontaneous abortion indicator</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>C130195</t>
+          <t>C64823</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>RNLANUM</t>
+          <t>MONO</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Number of Renal Arteries</t>
+          <t>Monocyte Count</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Number of Renal Arteries;RNLANUM</t>
+          <t>Monocytes</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>RNLANUM</t>
+          <t>MONO; Monocytes</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: number of renal arteries</t>
+          <t>GREEN_ONLY: mono</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>C130196</t>
+          <t>C64830</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>RNLVNUM</t>
+          <t>NEUTB</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Number of Renal Veins</t>
+          <t>Neutrophil Band Form Count</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Number of Renal Veins;RNLVNUM</t>
+          <t>Neutrophil Bands;Bands;NEUTB</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>RNLVNUM</t>
+          <t>Bands; NEUTB; Neutrophil Bands; Neutrophils Band Form</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: number of renal veins</t>
+          <t>GREEN_ONLY: neutrophils band form</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>C120837</t>
+          <t>C147406</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>SPABORTN</t>
+          <t>NORNCTN</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Number of Spontaneous Abortions</t>
+          <t>Nornicotine Measurement</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -4341,108 +4287,108 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>SPABORTN</t>
+          <t>Nornicotine</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Number of Miscarriages; SPABORTN</t>
+          <t>NORNCTN; Nornicotine</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: number of miscarriages</t>
+          <t>GREEN_ONLY: nornctn</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>C122393</t>
+          <t>C106551</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>EDUYRNUM</t>
+          <t>PREGNN</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Number of Years of Education</t>
+          <t>Number of Pregnancies</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>EDUYRNUM;Education</t>
+          <t>PREGNN;Maternal Gravity;Pregnancy Count;Total Number of Pregnancies</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>EDUYRNUM</t>
+          <t>Maternal Gravity; PREGNN; Total Number of Pregnancies; number of pregnancies; number_of_pregnancies; pregnancy count; pregnancy_count</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: education</t>
+          <t>GREEN_ONLY: number of pregnancies ; number_of_pregnancies ; pregnancy_count</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>C60832</t>
+          <t>C130195</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>OXYSAT</t>
+          <t>RNLANUM</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Oxygen Saturation Measurement</t>
+          <t>Number of Renal Arteries</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>SpO2;OXYSAT;O2 Saturation;Hemoglobin Saturation;Oximetry</t>
+          <t>Number of Renal Arteries;RNLANUM</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Blood Oxygen Saturation; Hemoglobin Saturation; Hemoglobin Saturation Measurement; O2 Saturation; OXYSAT; Oximetry; Oxygen Content Measurement; Oxygen Saturation; Vital Signs – Oxygen Saturation; oxygen saturation test</t>
+          <t>RNLANUM</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: blood oxygen saturation ; hemoglobin saturation measurement ; oxygen content measurement ; oxygen saturation ; oxygen saturation test ; vital signs – oxygen saturation ||| YELLOW_ONLY: spo2</t>
+          <t>YELLOW_ONLY: number of renal arteries</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>C119293</t>
+          <t>C130196</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>PO2FIO2</t>
+          <t>RNLVNUM</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Partial Pressure Arterial Oxygen to Fraction Inspired Oxygen Ratio Measurement</t>
+          <t>Number of Renal Veins</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -4452,34 +4398,34 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Horowitz Index;Carrico index;P/F ratio;Partial Pressure Arterial Oxygen to Fraction Inspired Oxygen Ratio Measurement;PO2FIO2;PAO2/FIO2;PP Arterial O2/Fraction Inspired O2</t>
+          <t>Number of Renal Veins;RNLVNUM</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>PAO2/FIO2; PO2FIO2; PP Arterial O2/Fraction Inspired O2</t>
+          <t>RNLVNUM</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: carrico index ; horowitz index ; p/f ratio ; partial pressure arterial oxygen to fraction inspired oxygen ratio measurement</t>
+          <t>YELLOW_ONLY: number of renal veins</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>C71251</t>
+          <t>C120837</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>PO2</t>
+          <t>SPABORTN</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Partial Pressure of Oxygen Measurement</t>
+          <t>Number of Spontaneous Abortions</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -4489,71 +4435,71 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>PaO2;Partial Pressure O2;PO2</t>
+          <t>SPABORTN</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>PO2; PaO2; Partial Pressure O2; Partial Pressure Oxygen; Partial Pressure of Oxygen</t>
+          <t>Number of Miscarriages; SPABORTN</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: partial pressure of oxygen ; partial pressure oxygen</t>
+          <t>GREEN_ONLY: number of miscarriages</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>C64857</t>
+          <t>C122393</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>PHOS</t>
+          <t>EDUYRNUM</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Phosphate Measurement</t>
+          <t>Number of Years of Education</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Phosphorus;Phosphate</t>
+          <t>EDUYRNUM;Education</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>Inorganic Phosphate; PHOS; Phosphate; Phosphorus</t>
+          <t>EDUYRNUM</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: inorganic phosphate ; phos</t>
+          <t>YELLOW_ONLY: education</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>C51951</t>
+          <t>C60832</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>PLAT</t>
+          <t>OXYSAT</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Platelet Count</t>
+          <t>Oxygen Saturation Measurement</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -4563,71 +4509,71 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Thrombocytes;Platelets;Anucleated Thrombocytes</t>
+          <t>Blood Oxygen Saturation;Hemoglobin Saturation Measurement;Hemoglobin Saturation;O2 Saturation;Oximetry;Oxygen Content Measurement;Oxygen Saturation;OXYSAT;SpO2;Vital Signs - Oxygen Saturation</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Anucleated Thrombocytes; PLAT; Platelet count; Platelets</t>
+          <t>Blood Oxygen Saturation; Hemoglobin Saturation; Hemoglobin Saturation Measurement; O2 Saturation; OXYSAT; Oximetry; Oxygen Content Measurement; Oxygen Saturation; Vital Signs – Oxygen Saturation; oxygen saturation test</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: plat ; platelet count ||| YELLOW_ONLY: thrombocytes</t>
+          <t>GREEN_ONLY: oxygen saturation test ; vital signs – oxygen saturation ||| YELLOW_ONLY: spo2 ; vital signs - oxygen saturation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
-          <t>C90491</t>
+          <t>C119293</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>PRGOUT</t>
+          <t>PO2FIO2</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Pregnancy Outcome</t>
+          <t>Partial Pressure Arterial Oxygen to Fraction Inspired Oxygen Ratio Measurement</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>PRGOUT</t>
+          <t>Horowitz Index;Carrico index;P/F ratio;Partial Pressure Arterial Oxygen to Fraction Inspired Oxygen Ratio Measurement;PO2FIO2;PAO2/FIO2;PP Arterial O2/Fraction Inspired O2</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>PREGOUT; PRGOUT; pregnancy outcome; pregnancy_outcome</t>
+          <t>PAO2/FIO2; PO2FIO2; PP Arterial O2/Fraction Inspired O2</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: pregnancy outcome ; pregnancy_outcome ; pregout</t>
+          <t>YELLOW_ONLY: carrico index ; horowitz index ; p/f ratio ; partial pressure arterial oxygen to fraction inspired oxygen ratio measurement</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>C62656</t>
+          <t>C71251</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PO2</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Prothrombin Time</t>
+          <t>Partial Pressure of Oxygen Measurement</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
@@ -4637,219 +4583,219 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PaO2;Partial Pressure O2;PO2</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>PT; Prothrombin Time Test</t>
+          <t>PO2; PaO2; Partial Pressure O2; Partial Pressure Oxygen; Partial Pressure of Oxygen</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: prothrombin time test</t>
+          <t>GREEN_ONLY: partial pressure of oxygen ; partial pressure oxygen</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>C189437</t>
+          <t>C64857</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>PDFF</t>
+          <t>PHOS</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Proton Density Fat Fraction</t>
+          <t>Phosphate Measurement</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Fat Fraction by Proton Density;PDFF;Proton Density Fat Fraction</t>
+          <t>Phosphorus;Phosphate</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>Fat Fraction by Proton Density; PDFF</t>
+          <t>Inorganic Phosphate; PHOS; Phosphate; Phosphorus</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: proton density fat fraction</t>
+          <t>GREEN_ONLY: inorganic phosphate ; phos</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>C174285</t>
+          <t>C51951</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>QTCUNSAG</t>
+          <t>PLAT</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>QTc Correction Method Unspecified, Aggregate</t>
+          <t>Platelet Count</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>QTCUNSAG</t>
+          <t>Thrombocytes;Platelets;Anucleated Thrombocytes</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>QTCUNSAG; QTc Corr Method Unspecified, Aggregate</t>
+          <t>Anucleated Thrombocytes; PLAT; Platelet count; Platelets</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: qtc corr method unspecified, aggregate</t>
+          <t>GREEN_ONLY: plat ; platelet count ||| YELLOW_ONLY: thrombocytes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
-          <t>C174286</t>
+          <t>C90491</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>QTCUNSSB</t>
+          <t>PRGOUT</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>QTc Correction Method Unspecified, Single Beat</t>
+          <t>Pregnancy Outcome</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>QTc Corr Method Unspecified, Single Beat;QTc Correction Method Unspecified, Single Beat;QTCUNSSB</t>
+          <t>PRGOUT</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>QTCUNSSB; QTc Corr Method Unspecified, Single Beat</t>
+          <t>PREGOUT; PRGOUT; pregnancy outcome; pregnancy_outcome</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: qtc correction method unspecified, single beat</t>
+          <t>GREEN_ONLY: pregnancy outcome ; pregnancy_outcome ; pregout</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>C117792</t>
+          <t>C62656</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>RRSM</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>RR Interval Single Measurement</t>
+          <t>Prothrombin Time</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>RR Interval Single Measurement;RRSM</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>RR Interval, Single Measurement; RRSM</t>
+          <t>PT; Prothrombin Time Test</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: rr interval, single measurement ||| YELLOW_ONLY: rr interval single measurement</t>
+          <t>GREEN_ONLY: prothrombin time test</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
-          <t>C49678</t>
+          <t>C189437</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>RESP</t>
+          <t>PDFF</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Respiratory Rate</t>
+          <t>Proton Density Fat Fraction</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>RESP;RESPRATE</t>
+          <t>Fat Fraction by Proton Density;PDFF;Proton Density Fat Fraction</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>RESP; RESPRATE; Respiratory rate; Vital Signs – Respiratory Rate; respiration rate; respiration_rate</t>
+          <t>Fat Fraction by Proton Density; PDFF</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: respiration rate ; respiration_rate ; respiratory rate ; vital signs – respiratory rate</t>
+          <t>YELLOW_ONLY: proton density fat fraction</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>C94535</t>
+          <t>C100945</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>NTRGRESP</t>
+          <t>PULSEPR</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Response in Non-Target Lesion</t>
+          <t>Pulse Pressure</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -4859,34 +4805,34 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>NTRGRESP;Non-Target Response</t>
+          <t>PULSEPR</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>NTRGRESP; Non-Target Lesions; Non-Target Response</t>
+          <t>PULSEPR; Pulse pressure</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: non-target lesions</t>
+          <t>GREEN_ONLY: pulse pressure</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
         <is>
-          <t>C94534</t>
+          <t>C174285</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>TRGRESP</t>
+          <t>QTCUNSAG</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Response in Target Lesion</t>
+          <t>QTc Correction Method Unspecified, Aggregate</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -4896,71 +4842,71 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>TRGRESP;Target Response</t>
+          <t>QTCUNSAG</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>LESION_RESPONSE; TRGRESP; Target Lesions; Target Response</t>
+          <t>QTCUNSAG; QTc Corr Method Unspecified, Aggregate</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: lesion_response ; target lesions</t>
+          <t>GREEN_ONLY: qtc corr method unspecified, aggregate</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>C81997</t>
+          <t>C174286</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>NEUTSG</t>
+          <t>QTCUNSSB</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Segmented Neutrophil Count</t>
+          <t>QTc Correction Method Unspecified, Single Beat</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Segmented Neutrophils;NEUTSG</t>
+          <t>QTc Corr Method Unspecified, Single Beat;QTc Correction Method Unspecified, Single Beat;QTCUNSSB</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>NEUTSG; Neutrophils, Segmented; Segmented Neutrophil; Segs (Neutrophils)</t>
+          <t>QTCUNSSB; QTc Corr Method Unspecified, Single Beat</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: neutrophils, segmented ; segmented neutrophil ; segs (neutrophils) ||| YELLOW_ONLY: segmented neutrophils</t>
+          <t>YELLOW_ONLY: qtc correction method unspecified, single beat</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
         <is>
-          <t>C82045</t>
+          <t>C117792</t>
         </is>
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>NEUTSGLE</t>
+          <t>RRSM</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Segmented Neutrophil to Leukocyte Ratio Measurement</t>
+          <t>RR Interval Single Measurement</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -4970,256 +4916,256 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Segmented Neutrophils/Leukocytes;NEUTSGLE</t>
+          <t>RR Interval Single Measurement;RRSM</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>NEUTSGLE; Neutrophils, Segmented/Leukocytes</t>
+          <t>RR Interval, Single Measurement; RRSM</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: neutrophils, segmented/leukocytes ||| YELLOW_ONLY: segmented neutrophils/leukocytes</t>
+          <t>GREEN_ONLY: rr interval, single measurement ||| YELLOW_ONLY: rr interval single measurement</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>C171532</t>
+          <t>C49678</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>SARSCOV2</t>
+          <t>RESP</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Severe Acute Respiratory Syndrome Coronavirus 2 Measurement</t>
+          <t>Respiratory Rate</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>SARSCOV2;SARS-CoV-2 Infection;COVID-19 Infection</t>
+          <t>RESP;RESPRATE</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>SARS-CoV-2; SARS-CoV-2 Measurement; SARSCOV2; Severe Acute Resp Syndrome Coronavirus 2; Severe Acute Respiratory Syndrome Coronavirus 2</t>
+          <t>RESP; RESPRATE; Respiratory rate; Vital Signs – Respiratory Rate; respiration rate; respiration_rate</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: sars-cov-2 ; sars-cov-2 measurement ; severe acute resp syndrome coronavirus 2 ; severe acute respiratory syndrome coronavirus 2 ||| YELLOW_ONLY: covid-19 infection ; sars-cov-2 infection</t>
+          <t>GREEN_ONLY: respiration rate ; respiration_rate ; respiratory rate ; vital signs – respiratory rate</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>C117776</t>
+          <t>C94535</t>
         </is>
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>PWDURSB</t>
+          <t>NTRGRESP</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Single Beat P Wave Duration</t>
+          <t>Response in Non-Target Lesion</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>P Wave Duration, Single Beat;Single Beat P Wave Duration;PWDURSB</t>
+          <t>NTRGRESP;Non-Target Response</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>P Wave Duration, Single Beat; PWDURSB</t>
+          <t>NTRGRESP; Non-Target Lesions; Non-Target Response</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: single beat p wave duration</t>
+          <t>GREEN_ONLY: non-target lesions</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>C117774</t>
+          <t>C94534</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>PRSB</t>
+          <t>TRGRESP</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Single Beat PR Interval</t>
+          <t>Response in Target Lesion</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Single Beat PR Interval;PQ Interval, Single Beat;PQSB;PR Interval, Single Beat;PR Interval, Single Beat;PRSB</t>
+          <t>TRGRESP;Target Response</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>PQ Interval, Single Beat; PQSB; PR Interval, Single Beat; PRSB</t>
+          <t>LESION_RESPONSE; TRGRESP; Target Lesions; Target Response</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: single beat pr interval</t>
+          <t>GREEN_ONLY: lesion_response ; target lesions</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>C117780</t>
+          <t>C81997</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>QRSSB</t>
+          <t>NEUTSG</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Single Beat QRS Duration</t>
+          <t>Segmented Neutrophil Count</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>QRS Duration, Single Beat;Single Beat QRS Duration;QRSSB</t>
+          <t>Segmented Neutrophils;NEUTSG</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>QRS Duration, Single Beat; QRSSB</t>
+          <t>NEUTSG; Neutrophils, Segmented; Segmented Neutrophil; Segs (Neutrophils)</t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: single beat qrs duration</t>
+          <t>GREEN_ONLY: neutrophils, segmented ; segmented neutrophil ; segs (neutrophils) ||| YELLOW_ONLY: segmented neutrophils</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>C117788</t>
+          <t>C82045</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>QTSB</t>
+          <t>NEUTSGLE</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Single Beat QT Interval</t>
+          <t>Segmented Neutrophil to Leukocyte Ratio Measurement</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>QT Interval, Single Beat;Single Beat QT Interval;QTSB</t>
+          <t>Segmented Neutrophils/Leukocytes;NEUTSGLE</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>QT Interval, Single Beat; QTSB</t>
+          <t>NEUTSGLE; Neutrophils, Segmented/Leukocytes</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: single beat qt interval</t>
+          <t>GREEN_ONLY: neutrophils, segmented/leukocytes ||| YELLOW_ONLY: segmented neutrophils/leukocytes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>C117785</t>
+          <t>C171532</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>QTCBSB</t>
+          <t>SARSCOV2</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Single Beat QTCB Interval</t>
+          <t>Severe Acute Respiratory Syndrome Coronavirus 2 Measurement</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>QTcB Interval, Single Beat;Single Beat QTCB Interval;QTCBSB</t>
+          <t>SARSCOV2;SARS-CoV-2 Infection;COVID-19 Infection</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>QTCBSB; QTcB Interval, Single Beat</t>
+          <t>SARS-CoV-2; SARS-CoV-2 Measurement; SARSCOV2; Severe Acute Resp Syndrome Coronavirus 2; Severe Acute Respiratory Syndrome Coronavirus 2</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: single beat qtcb interval</t>
+          <t>GREEN_ONLY: sars-cov-2 ; sars-cov-2 measurement ; severe acute resp syndrome coronavirus 2 ; severe acute respiratory syndrome coronavirus 2 ||| YELLOW_ONLY: covid-19 infection ; sars-cov-2 infection</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>C117787</t>
+          <t>C117776</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>QTCFSB</t>
+          <t>PWDURSB</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Single Beat QTCF Interval</t>
+          <t>Single Beat P Wave Duration</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
@@ -5229,34 +5175,34 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>QTcF Interval, Single Beat;QTCFSB;Single Beat QTCF Interval</t>
+          <t>P Wave Duration, Single Beat;Single Beat P Wave Duration;PWDURSB</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>QTCFSB; QTcF Interval, Single Beat</t>
+          <t>P Wave Duration, Single Beat; PWDURSB</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: single beat qtcf interval</t>
+          <t>YELLOW_ONLY: single beat p wave duration</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>C117772</t>
+          <t>C117774</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>PPSM</t>
+          <t>PRSB</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Single Measurement PP Interval</t>
+          <t>Single Beat PR Interval</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
@@ -5266,34 +5212,34 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>PP Interval, Single Measurement;Single Measurement PP Interval;PPSM</t>
+          <t>Single Beat PR Interval;PQ Interval, Single Beat;PQSB;PR Interval, Single Beat;PR Interval, Single Beat;PRSB</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>PP Interval, Single Measurement; PPSM</t>
+          <t>PQ Interval, Single Beat; PQSB; PR Interval, Single Beat; PRSB</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: single measurement pp interval</t>
+          <t>YELLOW_ONLY: single beat pr interval</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>C64809</t>
+          <t>C117780</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>SODIUM</t>
+          <t>QRSSB</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Sodium Measurement</t>
+          <t>Single Beat QRS Duration</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
@@ -5303,34 +5249,34 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Sodium;NA</t>
+          <t>QRS Duration, Single Beat;Single Beat QRS Duration;QRSSB</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
         <is>
-          <t>SODIUM</t>
+          <t>QRS Duration, Single Beat; QRSSB</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: na</t>
+          <t>YELLOW_ONLY: single beat qrs duration</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>C179824</t>
+          <t>C117788</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>SGDMGIND</t>
+          <t>QTSB</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Surgical Damage Indicator</t>
+          <t>Single Beat QT Interval</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
@@ -5340,219 +5286,219 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>SGDMGIND;Surgical Damage Indicator</t>
+          <t>QT Interval, Single Beat;Single Beat QT Interval;QTSB</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>SGDMGIND</t>
+          <t>QT Interval, Single Beat; QTSB</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: surgical damage indicator</t>
+          <t>YELLOW_ONLY: single beat qt interval</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>C25298</t>
+          <t>C117785</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>SYSBP</t>
+          <t>QTCBSB</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Systolic Blood Pressure</t>
+          <t>Single Beat QTCB Interval</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>SYSBP</t>
+          <t>QTcB Interval, Single Beat;Single Beat QTCB Interval;QTCBSB</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>SYSBP; Systolic Pressure; Systolic blood pressure; systolic bp; systolic_bp</t>
+          <t>QTCBSB; QTcB Interval, Single Beat</t>
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: systolic blood pressure ; systolic bp ; systolic pressure ; systolic_bp</t>
+          <t>YELLOW_ONLY: single beat qtcb interval</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
-          <t>C122157</t>
+          <t>C117787</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>TLYCE</t>
+          <t>QTCFSB</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>T-Lymphocyte Count</t>
+          <t>Single Beat QTCF Interval</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>T-Cell Lymphocytes;T-Cells;T-Lymphocytes</t>
+          <t>QTcF Interval, Single Beat;QTCFSB;Single Beat QTCF Interval</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
         <is>
-          <t>T Cells; T-Cell Count; T-Cell Lymphocytes; T-Cells; T-Lymphocytes; TLYCE</t>
+          <t>QTCFSB; QTcF Interval, Single Beat</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: t cells ; t-cell count ; tlyce</t>
+          <t>YELLOW_ONLY: single beat qtcf interval</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
-          <t>C41145</t>
+          <t>C117772</t>
         </is>
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>THICK</t>
+          <t>PPSM</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Thickness</t>
+          <t>Single Measurement PP Interval</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>THICK</t>
+          <t>PP Interval, Single Measurement;Single Measurement PP Interval;PPSM</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
         <is>
-          <t>THCKN; THICK; THICKNSS</t>
+          <t>PP Interval, Single Measurement; PPSM</t>
         </is>
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: thckn ; thicknss</t>
+          <t>YELLOW_ONLY: single measurement pp interval</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
-          <t>C64813</t>
+          <t>C64809</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>SODIUM</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Thyrotropin Measurement</t>
+          <t>Sodium Measurement</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>TSH;Thyrotropin</t>
+          <t>Sodium;NA</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>TSH; Thyroid Stimulating Hormone; Thyroid Stimulating Hormone Measurement; Thyrotropin</t>
+          <t>SODIUM</t>
         </is>
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: thyroid stimulating hormone ; thyroid stimulating hormone measurement</t>
+          <t>YELLOW_ONLY: na</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>C38037</t>
+          <t>C179824</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>BILI</t>
+          <t>SGDMGIND</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Total Bilirubin Measurement</t>
+          <t>Surgical Damage Indicator</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Yellow_Superset</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Bilirubin;Total Bilirubin Level</t>
+          <t>SGDMGIND;Surgical Damage Indicator</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>BILI; Bilirubin; Total Bilirubin; Total Bilirubin Level</t>
+          <t>SGDMGIND</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: bili ; total bilirubin</t>
+          <t>YELLOW_ONLY: surgical damage indicator</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
-          <t>C64858</t>
+          <t>C25298</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>PROT</t>
+          <t>SYSBP</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Total Protein Measurement</t>
+          <t>Systolic Blood Pressure</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
@@ -5562,34 +5508,34 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Protein</t>
+          <t>SYSBP</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>PROT; Protein; Total Protein</t>
+          <t>SYSBP; Systolic Pressure; Systolic blood pressure; systolic bp; systolic_bp</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: prot ; total protein</t>
+          <t>GREEN_ONLY: systolic blood pressure ; systolic bp ; systolic pressure ; systolic_bp</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>C17208</t>
+          <t>C122157</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>TRNSCPTN</t>
+          <t>TLYCE</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Transcription</t>
+          <t>T-Lymphocyte Count</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
@@ -5599,71 +5545,71 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>TRNSCPTN;RNA Expression;Genetic Transcription;Transcriptional</t>
+          <t>T-Cell Lymphocytes;T-Cells;T-Lymphocytes</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>Gene Transcription; Genetic Transcription; RNA Expression; TRNSCPTN; Transcriptional; transcription</t>
+          <t>T Cells; T-Cell Count; T-Cell Lymphocytes; T-Cells; T-Lymphocytes; TLYCE</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: gene transcription ; transcription</t>
+          <t>GREEN_ONLY: t cells ; t-cell count ; tlyce</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8" t="inlineStr">
         <is>
-          <t>C198341</t>
+          <t>C41145</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>TPADNA</t>
+          <t>THICK</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Treponema pallidum DNA Measurement</t>
+          <t>Thickness</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>TPADNA;Syphilis DNA</t>
+          <t>THICK</t>
         </is>
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>TPADNA; Treponema pallidum DNA</t>
+          <t>THCKN; THICK; THICKNSS</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: treponema pallidum dna ||| YELLOW_ONLY: syphilis dna</t>
+          <t>GREEN_ONLY: thckn ; thicknss</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>C184647</t>
+          <t>C64813</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Treponema pallidum Measurement</t>
+          <t>Thyrotropin Measurement</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
@@ -5673,34 +5619,34 @@
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>TSH;Thyrotropin</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>TPA; Treponema pallidum</t>
+          <t>TSH; Thyroid Stimulating Hormone; Thyroid Stimulating Hormone Measurement; Thyrotropin</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: treponema pallidum</t>
+          <t>GREEN_ONLY: thyroid stimulating hormone ; thyroid stimulating hormone measurement</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
         <is>
-          <t>C64812</t>
+          <t>C38037</t>
         </is>
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>TRIG</t>
+          <t>BILI</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Triglyceride Measurement</t>
+          <t>Total Bilirubin Measurement</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -5710,34 +5656,34 @@
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>TRIG;Triglycerides</t>
+          <t>Bilirubin;Total Bilirubin Level</t>
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>TRIG; Triglycerides; Triglycerides Measurement</t>
+          <t>BILI; Bilirubin; Total Bilirubin; Total Bilirubin Level</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: triglycerides measurement</t>
+          <t>GREEN_ONLY: bili ; total bilirubin</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>C74747</t>
+          <t>C64858</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>PROT</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Triiodothyronine Measurement</t>
+          <t>Total Protein Measurement</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -5747,108 +5693,108 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>T3;Total T3</t>
+          <t>Protein</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>T3; Total T3; Triiodothyronine</t>
+          <t>PROT; Protein; Total Protein</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: triiodothyronine</t>
+          <t>GREEN_ONLY: prot ; total protein</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8" t="inlineStr">
         <is>
-          <t>C74748</t>
+          <t>C17208</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>T3UP</t>
+          <t>TRNSCPTN</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Triiodothyronine Uptake Measurement</t>
+          <t>Transcription</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Both_Unique</t>
+          <t>Green_Superset</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>T3UP;T3U;Triiodothyronine Resin Uptake</t>
+          <t>TRNSCPTN;RNA Expression;Genetic Transcription;Transcriptional</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>T3RU; T3U; T3UP; Triiodothyronine Uptake</t>
+          <t>Gene Transcription; Genetic Transcription; RNA Expression; TRNSCPTN; Transcriptional; transcription</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: t3ru ; triiodothyronine uptake ||| YELLOW_ONLY: triiodothyronine resin uptake</t>
+          <t>GREEN_ONLY: gene transcription ; transcription</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>C74749</t>
+          <t>C198341</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>TROPONI</t>
+          <t>TPADNA</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Troponin I Measurement</t>
+          <t>Treponema pallidum DNA Measurement</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Green_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>TROPONI</t>
+          <t>TPADNA;Syphilis DNA</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
         <is>
-          <t>TROPONI; Troponin I</t>
+          <t>TPADNA; Treponema pallidum DNA</t>
         </is>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: troponin i</t>
+          <t>GREEN_ONLY: treponema pallidum dna ||| YELLOW_ONLY: syphilis dna</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
         <is>
-          <t>C96642</t>
+          <t>C184647</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>TUSPLIT</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Tumor Fragmentation</t>
+          <t>Treponema pallidum Measurement</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
@@ -5858,34 +5804,34 @@
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>TUSPLIT;Tumor Split</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
-          <t>TUSPLIT; Tumor Mass Fragmentation; Tumor Split</t>
+          <t>TPA; Treponema pallidum</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: tumor mass fragmentation</t>
+          <t>GREEN_ONLY: treponema pallidum</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>C154881</t>
+          <t>C64812</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>ULCERIND</t>
+          <t>TRIG</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Ulcer Indicator</t>
+          <t>Triglyceride Measurement</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
@@ -5895,34 +5841,34 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>ULCERIND;Ulceration Indicator</t>
+          <t>TRIG;Triglycerides</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
         <is>
-          <t>ULCERIND; ulceration indicator; ulceration_indicator</t>
+          <t>TRIG; Triglycerides; Triglycerides Measurement</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: ulceration_indicator</t>
+          <t>GREEN_ONLY: triglycerides measurement</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
         <is>
-          <t>C125949</t>
+          <t>C74747</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>UREAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Urea Nitrogen Measurement</t>
+          <t>Triiodothyronine Measurement</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
@@ -5932,71 +5878,71 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Urea Nitrogen</t>
+          <t>T3;Total T3</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>UREAN; Urea Nitrogen</t>
+          <t>T3; Total T3; Triiodothyronine</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: urean</t>
+          <t>GREEN_ONLY: triiodothyronine</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>C198401</t>
+          <t>C74748</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>UREXAM</t>
+          <t>T3UP</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Urinary System Examination</t>
+          <t>Triiodothyronine Uptake Measurement</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Yellow_Superset</t>
+          <t>Both_Unique</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>UREXAM;Urinary System Examination</t>
+          <t>T3UP;T3U;Triiodothyronine Resin Uptake</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
         <is>
-          <t>UREXAM</t>
+          <t>T3RU; T3U; T3UP; Triiodothyronine Uptake</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>YELLOW_ONLY: urinary system examination</t>
+          <t>GREEN_ONLY: t3ru ; triiodothyronine uptake ||| YELLOW_ONLY: triiodothyronine resin uptake</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>C105589</t>
+          <t>C74749</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>VLDL</t>
+          <t>TROPONI</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Very Low Density Lipoprotein Cholesterol Measurement</t>
+          <t>Troponin I Measurement</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
@@ -6006,34 +5952,34 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>VLDL;VLDL Cholesterol</t>
+          <t>TROPONI</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>VLDL; VLDL Cholesterol; VLDL Cholesterol Measurement</t>
+          <t>TROPONI; Troponin I</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: vldl cholesterol measurement</t>
+          <t>GREEN_ONLY: troponin i</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>C112429</t>
+          <t>C154881</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>WHEALSZ</t>
+          <t>ULCERIND</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Wheal Size Measurement</t>
+          <t>Ulcer Indicator</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
@@ -6043,59 +5989,207 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>WHEALSZ</t>
+          <t>ULCERIND;Ulceration Indicator</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>WHEALSZ; Wheal Size</t>
+          <t>ULCERIND; ulceration indicator; ulceration_indicator</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>GREEN_ONLY: wheal size</t>
+          <t>GREEN_ONLY: ulceration_indicator</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
+          <t>C125949</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>UREAN</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>Urea Nitrogen Measurement</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>Green_Superset</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>Urea Nitrogen</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>UREAN; Urea Nitrogen</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>GREEN_ONLY: urean</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>C198401</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>UREXAM</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>Urinary System Examination</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>Yellow_Superset</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>UREXAM;Urinary System Examination</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>UREXAM</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>YELLOW_ONLY: urinary system examination</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>C105589</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>VLDL</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Very Low Density Lipoprotein Cholesterol Measurement</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>Green_Superset</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>VLDL;VLDL Cholesterol</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>VLDL; VLDL Cholesterol; VLDL Cholesterol Measurement</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>GREEN_ONLY: vldl cholesterol measurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>C112429</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>WHEALSZ</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>Wheal Size Measurement</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>Green_Superset</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>WHEALSZ</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>WHEALSZ; Wheal Size</t>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>GREEN_ONLY: wheal size</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
           <t>C45997</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="D129" s="8" t="inlineStr">
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>Green_Superset</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
+      <c r="E133" s="8" t="inlineStr">
         <is>
           <t>PH;potential of Hydrogen</t>
         </is>
       </c>
-      <c r="F129" s="8" t="inlineStr">
+      <c r="F133" s="8" t="inlineStr">
         <is>
           <t>PH; [pH]; potential of Hydrogen</t>
         </is>
       </c>
-      <c r="G129" s="8" t="inlineStr">
+      <c r="G133" s="8" t="inlineStr">
         <is>
           <t>GREEN_ONLY: [ph]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G129"/>
+  <autoFilter ref="A1:G133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6106,7 +6200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12464,17 +12558,17 @@
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>C201227</t>
+          <t>C94525</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>MICROCY</t>
+          <t>TUMERGE</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Microcyte to Erythrocyte Ratio Measurement</t>
+          <t>Matted Tumor Mass Present</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
@@ -12489,34 +12583,34 @@
       </c>
       <c r="F152" s="8" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>Blood Cell Count Ratio Measurements; Erythrocyte Counts; Hematology Tests; Laboratory Tests</t>
+          <t>Oncology Standards; TU; Tumor/Lesion Identification</t>
         </is>
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>TU</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>C191153</t>
+          <t>C201227</t>
         </is>
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>RUTG0101</t>
+          <t>MICROCY</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Rutgeerts Score - Rutgeerts Score</t>
+          <t>Microcyte to Erythrocyte Ratio Measurement</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
@@ -12531,34 +12625,34 @@
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification; QRS; RUTG01; RUTGEERTS SCORE; Rutgeerts Score Clinical Classification; Rutgeerts Score Clinical Classification Question</t>
+          <t>Blood Cell Count Ratio Measurements; Erythrocyte Counts; Hematology Tests; Laboratory Tests</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>C73495</t>
+          <t>C191153</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>RUTG0101</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Serum HCG Measurement</t>
+          <t>Rutgeerts Score - Rutgeerts Score</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
@@ -12573,34 +12667,34 @@
       </c>
       <c r="F154" s="8" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>Chemistry Tests; Choriogonadotropin Measurements; HCG Measurements; Hormone Measurements; Laboratory Tests</t>
+          <t>Clinical or Research Assessment Classification; QRS; RUTG01; RUTGEERTS SCORE; Rutgeerts Score Clinical Classification; Rutgeerts Score Clinical Classification Question</t>
         </is>
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RS</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>C171439</t>
+          <t>C73495</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>SAR2AB</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Severe Acute Respiratory Syndrome Coronavirus 2 Antibody Measurement</t>
+          <t>Serum HCG Measurement</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
@@ -12615,34 +12709,34 @@
       </c>
       <c r="F155" s="8" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>COVID-19 Tests; Laboratory Tests; Microbiology Tests; SARS-CoV-2 Tests; Virology Tests</t>
+          <t>Chemistry Tests; Choriogonadotropin Measurements; HCG Measurements; Hormone Measurements; Laboratory Tests</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>C124716</t>
+          <t>C171439</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>TANN0201</t>
+          <t>SAR2AB</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy - Genitalia Stages</t>
+          <t>Severe Acute Respiratory Syndrome Coronavirus 2 Antibody Measurement</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
@@ -12657,34 +12751,34 @@
       </c>
       <c r="F156" s="8" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification; QRS; TANN02; TANNER SCALE BOY; Tanner Scale Boy Version; Tanner Scale-Boy; Tanner Scale-Boy Clinical Classification Question</t>
+          <t>COVID-19 Tests; Laboratory Tests; Microbiology Tests; SARS-CoV-2 Tests; Virology Tests</t>
         </is>
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>MB</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>C124717</t>
+          <t>C124716</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>TANN0202</t>
+          <t>TANN0201</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Tanner Scale-Boy - Pubic Hair Stages</t>
+          <t>Tanner Scale-Boy - Genitalia Stages</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr">
@@ -12716,17 +12810,17 @@
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>C124718</t>
+          <t>C124717</t>
         </is>
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>TANN0101</t>
+          <t>TANN0202</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl - Breast Stages</t>
+          <t>Tanner Scale-Boy - Pubic Hair Stages</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
@@ -12746,7 +12840,7 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>Clinical or Research Assessment Classification; QRS; TANN01; TANNER SCALE GIRL; Tanner Scale Girl Version; Tanner Scale Girl Version; Tanner Scale-Girl; Tanner Scale-Girl Clinical Classification Question</t>
+          <t>Clinical or Research Assessment Classification; QRS; TANN02; TANNER SCALE BOY; Tanner Scale Boy Version; Tanner Scale-Boy; Tanner Scale-Boy Clinical Classification Question</t>
         </is>
       </c>
       <c r="H158" s="8" t="inlineStr">
@@ -12758,17 +12852,17 @@
     <row r="159">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>C124719</t>
+          <t>C124718</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>TANN0102</t>
+          <t>TANN0101</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Tanner Scale-Girl - Pubic Hair Stages</t>
+          <t>Tanner Scale-Girl - Breast Stages</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
@@ -12800,47 +12894,131 @@
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
         <is>
+          <t>C124719</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>TANN0102</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t>Tanner Scale-Girl - Pubic Hair Stages</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>DSS</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>Clinical or Research Assessment Classification; QRS; TANN01; TANNER SCALE GIRL; Tanner Scale Girl Version; Tanner Scale Girl Version; Tanner Scale-Girl; Tanner Scale-Girl Clinical Classification Question</t>
+        </is>
+      </c>
+      <c r="H160" s="8" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
           <t>C132388</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>TPLAB</t>
         </is>
       </c>
-      <c r="C160" s="8" t="inlineStr">
+      <c r="C161" s="8" t="inlineStr">
         <is>
           <t>Treponema pallidum Antibody Measurement</t>
         </is>
       </c>
-      <c r="D160" s="8" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="E160" s="8" t="inlineStr">
-        <is>
-          <t>DSS</t>
-        </is>
-      </c>
-      <c r="F160" s="8" t="inlineStr">
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t>DSS</t>
+        </is>
+      </c>
+      <c r="F161" s="8" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
       </c>
-      <c r="G160" s="8" t="inlineStr">
+      <c r="G161" s="8" t="inlineStr">
         <is>
           <t>Antibody Measurements; Immunology Tests; Laboratory Tests; Microbiology Tests</t>
         </is>
       </c>
-      <c r="H160" s="8" t="inlineStr">
+      <c r="H161" s="8" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>C96642</t>
+        </is>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>TUSPLIT</t>
+        </is>
+      </c>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>Tumor Fragmentation</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="E162" s="8" t="inlineStr">
+        <is>
+          <t>DSS</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t>Oncology Standards; TU; Tumor/Lesion Identification</t>
+        </is>
+      </c>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H160"/>
+  <autoFilter ref="A1:H162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>